--- a/resources/library/xlsx/90-day-turnaround-plan.xlsx
+++ b/resources/library/xlsx/90-day-turnaround-plan.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" r:id="R7564d82face44c88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R85d700107a3942c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="Re8483e390bd74a30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" r:id="R1c2933557c784844"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R9e89be684ada4cab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="Rb97e955cc08e4cbd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -170,6 +170,102 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="272a2b8b-74bd-4657-a817-e877f83d6330"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R8cd91a576042438f"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="54da4d83-a3ba-4931-9e61-4fa4e0f3b899"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re9dbf69da92b4a34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="7c5a2720-f6a9-4081-82fc-13dad30b65aa"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rdfa9fbe6b6a14f66"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -380,7 +476,7 @@
     <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
@@ -1507,6 +1603,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c737a2e22ec4bc8"/>
 </x:worksheet>
 </file>
 
@@ -1521,7 +1618,7 @@
     <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
@@ -2577,6 +2674,7 @@
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bf33031f2db4e34"/>
 </x:worksheet>
 </file>
 
@@ -2591,7 +2689,7 @@
     <x:col min="2" max="2" width="80" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
@@ -3657,5 +3755,6 @@
     <x:mergeCell ref="A5:H5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce65d919b39b4356"/>
 </x:worksheet>
 </file>